--- a/store/Jun-2026/Mail Attachment/LinkedIn_Report_03-Jun-2026.xlsx
+++ b/store/Jun-2026/Mail Attachment/LinkedIn_Report_03-Jun-2026.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,7 +629,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>New Booking</t>
+          <t>Dispatched</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -647,32 +647,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910381</t>
+          <t>WTI-20260603-3910576</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
+          <t>LinkedIn Technology Information Private Limited – MUM</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MR.CHIRAG PILKHWAL</t>
+          <t>ANURADHA RAY</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-06-03 20:00:00</t>
+          <t>2026-06-03 19:45:00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8146662428</t>
+          <t>9819717303</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>cpilkhwal@linkedin.com</t>
+          <t>anray@linkedin.com</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -682,17 +682,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Dispatched</t>
+          <t>New Booking</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>BLR Hub</t>
+          <t>Mumbai Hub</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2704</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -700,7 +700,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910519</t>
+          <t>WTI-20260603-3910381</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -710,22 +710,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MR.AMAN PANDEY</t>
+          <t>MR.CHIRAG PILKHWAL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-04 02:00:00</t>
+          <t>2026-06-03 20:00:00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8005867409</t>
+          <t>8146662428</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ampandey@linkedin.com</t>
+          <t>cpilkhwal@linkedin.com</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>New Booking</t>
+          <t>Dispatched</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>2704</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -753,32 +753,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910460</t>
+          <t>WTI-20260603-3910519</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited – MUM</t>
+          <t>LinkedIn Technology Information Private Limited-BLR</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MS.AMRITA GHASGHASE</t>
+          <t>MR.AMAN PANDEY</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-04 03:00:00</t>
+          <t>2026-06-04 02:00:00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9930350785</t>
+          <t>8005867409</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>aghasghase@linkedin.com</t>
+          <t>ampandey@linkedin.com</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Pune Hub 1</t>
+          <t>BLR Hub</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -806,32 +806,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910475</t>
+          <t>WTI-20260603-3910460</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
+          <t>LinkedIn Technology Information Private Limited – MUM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MS.VAAGISHA</t>
+          <t>MS.AMRITA GHASGHASE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-04 08:45:00</t>
+          <t>2026-06-04 03:00:00</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>9818235942</t>
+          <t>9930350785</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>vaav@linkedin.com</t>
+          <t>aghasghase@linkedin.com</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>BLR Hub</t>
+          <t>Pune Hub 1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -859,32 +859,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910535</t>
+          <t>WTI-20260603-3910549</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited – GGN</t>
+          <t>LinkedIn Technology Information Private Limited – MUM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MR.GAUTAM SHARMA</t>
+          <t>SAUMITRA PIMPALKHARE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-04 08:45:00</t>
+          <t>2026-06-04 08:30:00</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8800020988</t>
+          <t>9108240923</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>gautsharma@linkedin.com</t>
+          <t>spimpalkhare@linkedin.com</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -899,12 +899,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Gurugram</t>
+          <t>Pune Hub 1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2311</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -912,32 +912,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910369</t>
+          <t>WTI-20260603-3910535</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
+          <t>LinkedIn Technology Information Private Limited – GGN</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MS.ASHIMA PALAHA</t>
+          <t>MR.GAUTAM SHARMA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-04 09:00:00</t>
+          <t>2026-06-04 08:45:00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6364527610</t>
+          <t>8800020988</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>apalahababbar@linkedin.com</t>
+          <t>gautsharma@linkedin.com</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Ahmedabad Hub1</t>
+          <t>Gurugram</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2311</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -965,32 +965,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910506</t>
+          <t>WTI-20260603-3910475</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited – MUM</t>
+          <t>LinkedIn Technology Information Private Limited-BLR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AMRITA GHASGHASE</t>
+          <t>MS.VAAGISHA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-04 22:00:00</t>
+          <t>2026-06-04 08:45:00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9930350785</t>
+          <t>9818235942</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>aghasghase@linkedin.com</t>
+          <t>vaav@linkedin.com</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1005,12 +1005,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Pune Hub 1</t>
+          <t>BLR Hub</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1018,7 +1018,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910402</t>
+          <t>WTI-20260603-3910369</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1028,22 +1028,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KARTHIK A</t>
+          <t>MS.ASHIMA PALAHA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-05 01:00:00</t>
+          <t>2026-06-04 09:00:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7774019193</t>
+          <t>6364527610</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>karumugam@linkedin.com</t>
+          <t>apalahababbar@linkedin.com</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1058,12 +1058,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BLR Hub</t>
+          <t>Ahmedabad Hub1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1071,32 +1071,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910385</t>
+          <t>WTI-20260603-3910506</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
+          <t>LinkedIn Technology Information Private Limited – MUM</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SHUBHAM GUPTA</t>
+          <t>AMRITA GHASGHASE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-05 01:45:00</t>
+          <t>2026-06-04 22:00:00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8764066357</t>
+          <t>9930350785</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>shubhamgupta@linkedin.com</t>
+          <t>aghasghase@linkedin.com</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>BLR Hub</t>
+          <t>Pune Hub 1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>2732</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1124,7 +1124,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910394</t>
+          <t>WTI-20260603-3910402</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SABRY TOZIN</t>
+          <t>KARTHIK A</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-22 00:10:00</t>
+          <t>2026-06-05 01:00:00</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>+14159900995</t>
+          <t>7774019193</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>kwojnowski@linkedin.com</t>
+          <t>karumugam@linkedin.com</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1177,7 +1177,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910410</t>
+          <t>WTI-20260603-3910385</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1187,22 +1187,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KELLIE WOJNOWSKI +8</t>
+          <t>SHUBHAM GUPTA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-06-22 08:00:00</t>
+          <t>2026-06-05 01:45:00</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>+14084553273</t>
+          <t>8764066357</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>kwojnowski@linkedin.com</t>
+          <t>shubhamgupta@linkedin.com</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1230,7 +1230,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910411</t>
+          <t>WTI-20260603-3910394</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1240,17 +1240,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KELLIE WOJNOWSKI +8</t>
+          <t>SABRY TOZIN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-22 08:00:00</t>
+          <t>2026-06-22 00:10:00</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>+14084553273</t>
+          <t>+14159900995</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910412</t>
+          <t>WTI-20260603-3910410</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1336,7 +1336,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910413</t>
+          <t>WTI-20260603-3910411</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1389,7 +1389,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910416</t>
+          <t>WTI-20260603-3910412</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-06-23 08:00:00</t>
+          <t>2026-06-22 08:00:00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1442,7 +1442,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910417</t>
+          <t>WTI-20260603-3910413</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-23 08:00:00</t>
+          <t>2026-06-22 08:00:00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1495,7 +1495,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910418</t>
+          <t>WTI-20260603-3910416</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1548,7 +1548,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910419</t>
+          <t>WTI-20260603-3910417</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1601,7 +1601,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910420</t>
+          <t>WTI-20260603-3910418</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-24 08:00:00</t>
+          <t>2026-06-23 08:00:00</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1654,7 +1654,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910421</t>
+          <t>WTI-20260603-3910419</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-24 08:00:00</t>
+          <t>2026-06-23 08:00:00</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1707,7 +1707,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910422</t>
+          <t>WTI-20260603-3910420</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1760,7 +1760,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910423</t>
+          <t>WTI-20260603-3910421</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1813,7 +1813,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910424</t>
+          <t>WTI-20260603-3910422</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-25 08:00:00</t>
+          <t>2026-06-24 08:00:00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1866,7 +1866,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910425</t>
+          <t>WTI-20260603-3910423</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-25 08:00:00</t>
+          <t>2026-06-24 08:00:00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1919,7 +1919,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910426</t>
+          <t>WTI-20260603-3910424</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1972,7 +1972,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>WTI-20260603-3910427</t>
+          <t>WTI-20260603-3910425</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2025,55 +2025,161 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>WTI-20260603-3910426</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LinkedIn Technology Information Private Limited-BLR</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>KELLIE WOJNOWSKI +8</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-06-25 08:00:00</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>+14084553273</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>kwojnowski@linkedin.com</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>BLR Hub</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>5400</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>WTI-20260603-3910427</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LinkedIn Technology Information Private Limited-BLR</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>KELLIE WOJNOWSKI +8</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-06-25 08:00:00</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>+14084553273</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>kwojnowski@linkedin.com</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>BLR Hub</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>5400</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>WTI-20260603-3910397</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>LinkedIn Technology Information Private Limited-BLR</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>LinkedIn Technology Information Private Limited-BLR</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>SABRY TOZIN VIANNE SHAH KARENA LEE</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>2026-06-25 22:00:00</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>+14159900995</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>kwojnowski@linkedin.com</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>BTC</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>New Booking</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>BLR Hub</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>New Booking</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>BLR Hub</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>5400</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
